--- a/public/data/gameData.xlsx
+++ b/public/data/gameData.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,82 +424,82 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MD NAIMUL ALAM</v>
+        <v>asdasd</v>
       </c>
       <c r="B2" t="str">
-        <v>naimul@gmail.com</v>
+        <v>example@example.com</v>
       </c>
       <c r="C2" t="str">
-        <v>0544800863</v>
+        <v>000-000-0000</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="str">
-        <v>00:29</v>
+        <v>00:34</v>
       </c>
       <c r="F2" t="str">
-        <v>★★★</v>
+        <v>★★☆</v>
       </c>
       <c r="G2" t="str">
-        <v>1/16/2026, 3:18:49 PM</v>
+        <v>1/23/2026, 3:15:23 PM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>asdas</v>
+        <v>Guest</v>
       </c>
       <c r="B3" t="str">
-        <v>asdas@gmail.com</v>
+        <v>example@example.com</v>
       </c>
       <c r="C3" t="str">
-        <v>564545</v>
+        <v>000-000-0000</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="str">
-        <v>00:32</v>
+        <v>00:37</v>
       </c>
       <c r="F3" t="str">
-        <v>★★★</v>
+        <v>★★☆</v>
       </c>
       <c r="G3" t="str">
-        <v>1/16/2026, 3:30:14 PM</v>
+        <v>1/23/2026, 3:17:09 PM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>NAIM</v>
+        <v>Zasda</v>
       </c>
       <c r="B4" t="str">
-        <v>naim@gmail.com</v>
+        <v>example@example.com</v>
       </c>
       <c r="C4" t="str">
-        <v>0544480054</v>
+        <v>000-000-0000</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>00:22</v>
+        <v>00:00</v>
       </c>
       <c r="F4" t="str">
-        <v>★★★</v>
+        <v>null</v>
       </c>
       <c r="G4" t="str">
-        <v>1/16/2026, 3:32:29 PM</v>
+        <v>1/23/2026, 3:19:07 PM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>sdfsd</v>
+        <v>MD NAIMUL ALAM</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>example@example.com</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>000-000-0000</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -511,18 +511,18 @@
         <v>null</v>
       </c>
       <c r="G5" t="str">
-        <v>1/16/2026, 3:34:10 PM</v>
+        <v>1/23/2026, 3:21:20 PM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>asd</v>
+        <v>adasda</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>example@example.com</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>000-000-0000</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -534,58 +534,219 @@
         <v>null</v>
       </c>
       <c r="G6" t="str">
-        <v>1/16/2026, 3:39:08 PM</v>
+        <v>1/23/2026, 3:35:11 PM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>NAIM</v>
+        <v>Guest</v>
       </c>
       <c r="B7" t="str">
-        <v>asdasd@gmail.com</v>
+        <v>example@example.com</v>
       </c>
       <c r="C7" t="str">
-        <v>541544</v>
+        <v>000-000-0000</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>00:20</v>
+        <v>00:00</v>
       </c>
       <c r="F7" t="str">
-        <v>★★★</v>
+        <v>null</v>
       </c>
       <c r="G7" t="str">
-        <v>1/16/2026, 4:04:51 PM</v>
+        <v>1/23/2026, 3:39:48 PM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AFRIN</v>
+        <v>Guest</v>
       </c>
       <c r="B8" t="str">
-        <v>afrin@gmail.com</v>
+        <v>example@example.com</v>
       </c>
       <c r="C8" t="str">
-        <v>0544800863</v>
+        <v>000-000-0000</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E8" t="str">
-        <v>00:21</v>
+        <v>00:00</v>
       </c>
       <c r="F8" t="str">
+        <v>null</v>
+      </c>
+      <c r="G8" t="str">
+        <v>1/23/2026, 3:43:00 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Guest</v>
+      </c>
+      <c r="B9" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="F9" t="str">
+        <v>null</v>
+      </c>
+      <c r="G9" t="str">
+        <v>1/23/2026, 3:49:01 PM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>asdasd</v>
+      </c>
+      <c r="B10" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="F10" t="str">
+        <v>null</v>
+      </c>
+      <c r="G10" t="str">
+        <v>1/23/2026, 3:50:33 PM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>asdasd</v>
+      </c>
+      <c r="B11" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C11" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="F11" t="str">
+        <v>null</v>
+      </c>
+      <c r="G11" t="str">
+        <v>1/23/2026, 3:52:21 PM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Guest</v>
+      </c>
+      <c r="B12" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C12" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="F12" t="str">
+        <v>null</v>
+      </c>
+      <c r="G12" t="str">
+        <v>1/23/2026, 3:57:51 PM</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>NAIM</v>
+      </c>
+      <c r="B13" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C13" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="F13" t="str">
+        <v>null</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1/23/2026, 4:00:12 PM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Guest</v>
+      </c>
+      <c r="B14" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C14" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="F14" t="str">
+        <v>null</v>
+      </c>
+      <c r="G14" t="str">
+        <v>1/23/2026, 4:13:42 PM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ALAM</v>
+      </c>
+      <c r="B15" t="str">
+        <v>example@example.com</v>
+      </c>
+      <c r="C15" t="str">
+        <v>000-000-0000</v>
+      </c>
+      <c r="D15">
+        <v>13</v>
+      </c>
+      <c r="E15" t="str">
+        <v>00:52</v>
+      </c>
+      <c r="F15" t="str">
         <v>★★★</v>
       </c>
-      <c r="G8" t="str">
-        <v>1/16/2026, 4:08:47 PM</v>
+      <c r="G15" t="str">
+        <v>1/23/2026, 4:17:12 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
   </ignoredErrors>
 </worksheet>
 </file>